--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,14 +770,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45163.60948461683</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="25">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -827,16 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="22.5" customHeight="1" s="25"/>
     <row r="24" ht="22.5" customHeight="1" s="25"/>
     <row r="25" ht="22.5" customHeight="1" s="25"/>
@@ -929,10 +915,8 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>***************</t>
-        </is>
+      <c r="D37" s="20" t="n">
+        <v>17717.317</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="18" customHeight="1" s="25">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="28" t="n"/>
@@ -965,35 +948,31 @@
     <row r="45" ht="19.5" customHeight="1" s="25">
       <c r="B45" s="24" t="n"/>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="19.5" customHeight="1" s="25">
       <c r="A48" s="6" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="n"/>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -959,20 +959,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -959,20 +959,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,10 +770,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45267</v>
+        <v>45259.55042783153</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="25">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -823,6 +827,16 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23" ht="22.5" customHeight="1" s="25"/>
     <row r="24" ht="22.5" customHeight="1" s="25"/>
     <row r="25" ht="22.5" customHeight="1" s="25"/>
@@ -884,7 +898,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="20" t="n">
-        <v>15097</v>
+        <v>23550</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="25">
@@ -900,7 +914,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="20" t="n">
-        <v>3375</v>
+        <v>5265</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="25">
@@ -915,8 +929,10 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="20" t="n">
-        <v>17717.317</v>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>***************</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -929,6 +945,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="18" customHeight="1" s="25">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="28" t="n"/>
@@ -948,31 +965,35 @@
     <row r="45" ht="19.5" customHeight="1" s="25">
       <c r="B45" s="24" t="n"/>
     </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48" ht="19.5" customHeight="1" s="25">
       <c r="A48" s="6" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="n"/>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,14 +770,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45259.55042783153</v>
+        <v>45273</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="25">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -827,16 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="22.5" customHeight="1" s="25"/>
     <row r="24" ht="22.5" customHeight="1" s="25"/>
     <row r="25" ht="22.5" customHeight="1" s="25"/>
@@ -898,7 +884,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="20" t="n">
-        <v>23550</v>
+        <v>28495.5</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="25">
@@ -914,7 +900,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="20" t="n">
-        <v>5265</v>
+        <v>6370.65</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="25">
@@ -945,7 +931,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="18" customHeight="1" s="25">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="28" t="n"/>
@@ -965,35 +950,31 @@
     <row r="45" ht="19.5" customHeight="1" s="25">
       <c r="B45" s="24" t="n"/>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="19.5" customHeight="1" s="25">
       <c r="A48" s="6" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="n"/>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45273</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="20" t="n">
-        <v>28495.5</v>
+        <v>15097</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="25">
@@ -900,7 +900,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="20" t="n">
-        <v>6370.65</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="25">
@@ -917,7 +917,7 @@
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>***************</t>
+          <t>********</t>
         </is>
       </c>
     </row>
@@ -961,20 +961,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45286</v>
+        <v>45287</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -961,20 +961,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS/mi/TENDEDERO CALESITA DISMAY.xlsx
@@ -961,20 +961,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
